--- a/output/pdf_financials_xlsx/AISX.xlsx
+++ b/output/pdf_financials_xlsx/AISX.xlsx
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.044799</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3590,19 +3590,19 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.152477</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.152477</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.152477</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.192407</v>
       </c>
     </row>
     <row r="93">
@@ -6172,7 +6172,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -8027,7 +8031,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -9178,7 +9186,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AISX.xlsx
+++ b/output/pdf_financials_xlsx/AISX.xlsx
@@ -795,16 +795,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.044393</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02992</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001864</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000319</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>-1.126538</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.126538</v>
+        <v>-1.170931</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.773797</v>
+        <v>-2.803717</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.838645</v>
+        <v>-2.840509</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.479745</v>
+        <v>-2.480064</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.620507</v>
@@ -1421,16 +1421,16 @@
         <v>-1.126538</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.126538</v>
+        <v>-1.170931</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.773797</v>
+        <v>-2.803717</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.838645</v>
+        <v>-2.840509</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.479745</v>
+        <v>-2.480064</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.620507</v>
@@ -1457,16 +1457,16 @@
         <v>-4059.596396396396</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-610.2589382448538</v>
+        <v>-634.3071505958829</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-814.4237544922838</v>
+        <v>-823.2086651163883</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1056.519117608745</v>
+        <v>-1057.212882287042</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-2364.093543835564</v>
+        <v>-2364.397666170918</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-3062.18253968254</v>
@@ -1562,19 +1562,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.08805399999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.595908</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.948299</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.359511</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.177392</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.140192</v>
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.08805399999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.595908</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.948299</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.359511</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.177392</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>1.140192</v>
@@ -2041,16 +2041,16 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.635298</v>
+        <v>0.03939</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.022668</v>
+        <v>0.074369</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.426726</v>
+        <v>0.067215</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.416734</v>
+        <v>0.239342</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.073102</v>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -24558,7 +24558,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -26069,7 +26069,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">

--- a/output/pdf_financials_xlsx/AISX.xlsx
+++ b/output/pdf_financials_xlsx/AISX.xlsx
@@ -625,19 +625,19 @@
         <v>0.08276699999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.153434</v>
+        <v>0.215434</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.041718</v>
+        <v>0.148218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.063864</v>
+        <v>0.165574</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.080294</v>
+        <v>0.195794</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.182922</v>
+        <v>0.191922</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.32713</v>
@@ -1109,10 +1109,10 @@
         <v>-2.773797</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-2.838645</v>
+        <v>-2.14071</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-2.479745</v>
+        <v>-2.051628</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.620507</v>
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.697935</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.428117</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -3857,31 +3857,31 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000541</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.009880999999999999</v>
+        <v>-0.041368</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.03964</v>
+        <v>-0.034339</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.013587</v>
+        <v>0.028145</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.084338</v>
+        <v>-0.06479799999999999</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.093707</v>
+        <v>0.077191</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.006765</v>
+        <v>-0.029334</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>-0.023814</v>
+        <v>-0.057894</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.023814</v>
+        <v>0.01661</v>
       </c>
     </row>
     <row r="102">
@@ -4027,31 +4027,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005415</v>
+        <v>0.004874</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.05979</v>
+        <v>0.028303</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.174062</v>
+        <v>0.179363</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.070103</v>
+        <v>-0.055545</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.121815</v>
+        <v>-0.102275</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.276942</v>
+        <v>0.260426</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.128512</v>
+        <v>-0.164611</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.258229</v>
+        <v>0.224149</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.002377</v>
+        <v>-0.009580999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.164484</v>
       </c>
     </row>
     <row r="111">
@@ -4200,25 +4200,25 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015497</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06791700000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01731</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009953</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.050539</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014753</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001749</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.270155</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -5028,25 +5028,25 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015497</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06791700000000001</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01731</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009953</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.050539</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014753</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001749</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -5062,25 +5062,25 @@
         <v>-0.000751</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.304578</v>
+        <v>-1.320075</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.718124</v>
+        <v>-2.786041</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.508721</v>
+        <v>-2.526031</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.701</v>
+        <v>-2.710953</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.939765</v>
+        <v>-2.990304</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.406311</v>
+        <v>-1.421064</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.148603</v>
+        <v>-1.150352</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.447501</v>
@@ -9670,7 +9670,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -10024,7 +10028,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -10669,7 +10677,11 @@
           <t>Acquisition of equipment 5</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -11499,7 +11511,11 @@
           <t>Shares issued for cash 8</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -12530,7 +12546,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -13049,7 +13069,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>-0.000541</v>
       </c>
@@ -13952,7 +13976,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -21905,7 +21933,11 @@
           <t>Directors' fees 11</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -22965,7 +22997,11 @@
           <t>Directors' fees 12</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -23787,7 +23823,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -23844,7 +23884,11 @@
           <t>Loss from discontinued operations 15</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -24617,7 +24661,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -25219,7 +25267,11 @@
           <t>Director's fees 12</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -25880,7 +25932,11 @@
           <t>Directors fees 12</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
